--- a/site/exports/dlut-humanities.xlsx
+++ b/site/exports/dlut-humanities.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -622,11 +622,65 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>李英杰</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>人文学院</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/369/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>仅官方个人履历，未独立目录核验，当前在职未知。；未出现本人导师姓名；硕士生导师是本人指导资格，不作为本人求学导师。；首次著作链接Cache miss，未取得具名作品；未换路或重试，作品0仅限本批。；原始HTTP、完整网页、学位证书未验证；保留必要摘录。；教育经历月份不认定毕业或授位月份。；来源差异/限制：个人信息及简介副教授；工作经历自2016.07至今列讲师，不合并为现职认证。；来源差异/限制：个人信息人文学院；简介人文与社会科学学部。各保留来源标签，未认证组织更名或现时归属。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -638,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -720,7 +774,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1546,8 +1600,274 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>李英杰</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>中央民族大学</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2005-09</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2009-07</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>哲学</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>明确授位语句支持授予；教育经历起止月份不转授位或毕业日期。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源unit：哲学与宗教学学院</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/369/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>李英杰</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2016-07</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>科学技术哲学</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>明确授位语句支持授予；教育经历起止月份不转授位或毕业日期。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源unit：社会科学学院科学技术与社会研究所</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/369/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>李英杰</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>博士期间学术交流</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>东京工业大学</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2012-09</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>该交流本身非授位，不否认清华博士学位。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源unit：社会理工研究科</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/369/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>李英杰</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>讲师</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2016-07</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（end_label_as_source）：至今</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/369/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S14"/>
+  <autoFilter ref="A1:S18"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1562,6 +1882,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1871,14 +2195,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="51.8" customWidth="1" min="2" max="2"/>
+    <col width="62.99999999999999" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="46.2" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2093,14 +2417,52 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>李英杰</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-dlut-liyingjie-s001-cff692148e8b</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.dlut.edu.cn/369/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T05:21:16Z</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>dlut</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/dlut-humanities.xlsx
+++ b/site/exports/dlut-humanities.xlsx
@@ -1641,7 +1641,7 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L15" s="2" t="b">
@@ -1712,7 +1712,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L16" s="2" t="b">
